--- a/grades.xlsx
+++ b/grades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ed07fd10c321503/01-NCAD/12-Grades/2026/SummerFinal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="8_{169B6E99-CE42-4446-8097-7602CA707B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C55155D-7874-4617-970F-7D6FC43FD057}"/>
+  <xr:revisionPtr revIDLastSave="123" documentId="8_{169B6E99-CE42-4446-8097-7602CA707B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88A3F61E-13CD-46D4-9640-F94BDD11D5A1}"/>
   <bookViews>
-    <workbookView xWindow="-24555" yWindow="540" windowWidth="24015" windowHeight="14910" xr2:uid="{812F6BAB-32B7-4A4D-B27F-99652F636AC8}"/>
+    <workbookView xWindow="-28200" yWindow="420" windowWidth="23565" windowHeight="15240" xr2:uid="{812F6BAB-32B7-4A4D-B27F-99652F636AC8}"/>
   </bookViews>
   <sheets>
     <sheet name="2025-06-22T1604_Grades-Summer_2" sheetId="1" r:id="rId1"/>
@@ -729,11 +729,11 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -791,6 +791,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1123,25 +1127,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1252,9 +1256,9 @@
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <f>P4</f>
-        <v>100.38000000000001</v>
+        <v>100.32</v>
       </c>
       <c r="C4" s="6">
         <v>6</v>
@@ -1275,15 +1279,18 @@
         <v>6</v>
       </c>
       <c r="I4" s="6">
+        <v>6</v>
+      </c>
+      <c r="J4" s="6">
         <v>6</v>
       </c>
       <c r="O4" s="6">
         <f t="shared" ref="O4:O31" si="0">C4+D4+E4+F4+G4+H4+I4+J4+K4+L4+M4+N4</f>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P4" s="7">
-        <f>O4*2.39</f>
-        <v>100.38000000000001</v>
+        <f>O4*2.09</f>
+        <v>100.32</v>
       </c>
       <c r="Q4" s="1" t="s">
         <v>36</v>
@@ -1293,9 +1300,9 @@
       <c r="A5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="8">
         <f t="shared" ref="B5:B31" si="1">P5</f>
-        <v>100.38000000000001</v>
+        <v>100.32</v>
       </c>
       <c r="C5" s="6">
         <v>6</v>
@@ -1318,13 +1325,16 @@
       <c r="I5" s="6">
         <v>6</v>
       </c>
+      <c r="J5" s="6">
+        <v>6</v>
+      </c>
       <c r="O5" s="6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P5" s="7">
-        <f t="shared" ref="P5:P31" si="2">O5*2.39</f>
-        <v>100.38000000000001</v>
+        <f t="shared" ref="P5:P31" si="2">O5*2.09</f>
+        <v>100.32</v>
       </c>
       <c r="Q5" s="1" t="s">
         <v>36</v>
@@ -1334,9 +1344,9 @@
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="9">
-        <f t="shared" si="1"/>
-        <v>100.38000000000001</v>
+      <c r="B6" s="8">
+        <f t="shared" si="1"/>
+        <v>100.32</v>
       </c>
       <c r="C6" s="6">
         <v>6</v>
@@ -1359,13 +1369,16 @@
       <c r="I6" s="6">
         <v>6</v>
       </c>
+      <c r="J6" s="6">
+        <v>6</v>
+      </c>
       <c r="O6" s="6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P6" s="7">
         <f t="shared" si="2"/>
-        <v>100.38000000000001</v>
+        <v>100.32</v>
       </c>
       <c r="Q6" s="1" t="s">
         <v>36</v>
@@ -1375,9 +1388,9 @@
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="9">
-        <f t="shared" si="1"/>
-        <v>86.04</v>
+      <c r="B7" s="8">
+        <f t="shared" si="1"/>
+        <v>87.78</v>
       </c>
       <c r="C7" s="6">
         <v>6</v>
@@ -1400,13 +1413,16 @@
       <c r="I7" s="6">
         <v>6</v>
       </c>
+      <c r="J7" s="6">
+        <v>6</v>
+      </c>
       <c r="O7" s="6">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="P7" s="7">
         <f t="shared" si="2"/>
-        <v>86.04</v>
+        <v>87.78</v>
       </c>
       <c r="Q7" s="1" t="s">
         <v>37</v>
@@ -1416,9 +1432,9 @@
       <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="9">
-        <f t="shared" si="1"/>
-        <v>86.04</v>
+      <c r="B8" s="8">
+        <f t="shared" si="1"/>
+        <v>87.78</v>
       </c>
       <c r="C8" s="6">
         <v>6</v>
@@ -1441,13 +1457,16 @@
       <c r="I8" s="6">
         <v>6</v>
       </c>
+      <c r="J8" s="6">
+        <v>6</v>
+      </c>
       <c r="O8" s="6">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="P8" s="7">
         <f t="shared" si="2"/>
-        <v>86.04</v>
+        <v>87.78</v>
       </c>
       <c r="Q8" s="1" t="s">
         <v>37</v>
@@ -1457,9 +1476,9 @@
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="9">
-        <f t="shared" si="1"/>
-        <v>100.38000000000001</v>
+      <c r="B9" s="8">
+        <f t="shared" si="1"/>
+        <v>100.32</v>
       </c>
       <c r="C9" s="6">
         <v>6</v>
@@ -1482,13 +1501,16 @@
       <c r="I9" s="6">
         <v>6</v>
       </c>
+      <c r="J9" s="6">
+        <v>6</v>
+      </c>
       <c r="O9" s="6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P9" s="7">
         <f t="shared" si="2"/>
-        <v>100.38000000000001</v>
+        <v>100.32</v>
       </c>
       <c r="Q9" s="1" t="s">
         <v>36</v>
@@ -1498,9 +1520,9 @@
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="9">
-        <f t="shared" si="1"/>
-        <v>100.38000000000001</v>
+      <c r="B10" s="8">
+        <f t="shared" si="1"/>
+        <v>100.32</v>
       </c>
       <c r="C10" s="6">
         <v>6</v>
@@ -1523,13 +1545,16 @@
       <c r="I10" s="6">
         <v>6</v>
       </c>
+      <c r="J10" s="6">
+        <v>6</v>
+      </c>
       <c r="O10" s="6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P10" s="7">
         <f t="shared" si="2"/>
-        <v>100.38000000000001</v>
+        <v>100.32</v>
       </c>
       <c r="Q10" s="1" t="s">
         <v>36</v>
@@ -1539,9 +1564,9 @@
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="9">
-        <f t="shared" si="1"/>
-        <v>71.7</v>
+      <c r="B11" s="8">
+        <f t="shared" si="1"/>
+        <v>62.699999999999996</v>
       </c>
       <c r="C11" s="6">
         <v>6</v>
@@ -1561,13 +1586,16 @@
       <c r="H11" s="6">
         <v>6</v>
       </c>
+      <c r="I11" s="6">
+        <v>0</v>
+      </c>
       <c r="O11" s="6">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="P11" s="7">
         <f t="shared" si="2"/>
-        <v>71.7</v>
+        <v>62.699999999999996</v>
       </c>
       <c r="Q11" s="1" t="s">
         <v>38</v>
@@ -1577,9 +1605,9 @@
       <c r="A12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="9">
-        <f t="shared" si="1"/>
-        <v>100.38000000000001</v>
+      <c r="B12" s="8">
+        <f t="shared" si="1"/>
+        <v>100.32</v>
       </c>
       <c r="C12" s="6">
         <v>6</v>
@@ -1602,13 +1630,16 @@
       <c r="I12" s="6">
         <v>6</v>
       </c>
+      <c r="J12" s="6">
+        <v>6</v>
+      </c>
       <c r="O12" s="6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P12" s="7">
         <f t="shared" si="2"/>
-        <v>100.38000000000001</v>
+        <v>100.32</v>
       </c>
       <c r="Q12" s="1" t="s">
         <v>36</v>
@@ -1618,9 +1649,9 @@
       <c r="A13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="9">
-        <f t="shared" si="1"/>
-        <v>71.7</v>
+      <c r="B13" s="8">
+        <f t="shared" si="1"/>
+        <v>75.239999999999995</v>
       </c>
       <c r="C13" s="6">
         <v>6</v>
@@ -1637,13 +1668,19 @@
       <c r="G13" s="6">
         <v>6</v>
       </c>
+      <c r="H13" s="6">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6">
+        <v>6</v>
+      </c>
       <c r="O13" s="6">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="P13" s="7">
         <f t="shared" si="2"/>
-        <v>71.7</v>
+        <v>75.239999999999995</v>
       </c>
       <c r="Q13" s="1" t="s">
         <v>37</v>
@@ -1653,9 +1690,9 @@
       <c r="A14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="9">
-        <f t="shared" si="1"/>
-        <v>71.7</v>
+      <c r="B14" s="8">
+        <f t="shared" si="1"/>
+        <v>75.239999999999995</v>
       </c>
       <c r="C14" s="6">
         <v>6</v>
@@ -1672,16 +1709,22 @@
       <c r="G14" s="6">
         <v>6</v>
       </c>
+      <c r="H14" s="6">
+        <v>0</v>
+      </c>
       <c r="I14" s="6">
         <v>6</v>
       </c>
+      <c r="J14" s="6">
+        <v>6</v>
+      </c>
       <c r="O14" s="6">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="P14" s="7">
         <f t="shared" si="2"/>
-        <v>71.7</v>
+        <v>75.239999999999995</v>
       </c>
       <c r="Q14" s="1" t="s">
         <v>37</v>
@@ -1691,9 +1734,9 @@
       <c r="A15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="9">
-        <f t="shared" si="1"/>
-        <v>100.38000000000001</v>
+      <c r="B15" s="8">
+        <f t="shared" si="1"/>
+        <v>100.32</v>
       </c>
       <c r="C15" s="6">
         <v>6</v>
@@ -1716,13 +1759,16 @@
       <c r="I15" s="6">
         <v>6</v>
       </c>
+      <c r="J15" s="6">
+        <v>6</v>
+      </c>
       <c r="O15" s="6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P15" s="7">
         <f t="shared" si="2"/>
-        <v>100.38000000000001</v>
+        <v>100.32</v>
       </c>
       <c r="Q15" s="1" t="s">
         <v>36</v>
@@ -1732,9 +1778,9 @@
       <c r="A16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="9">
-        <f t="shared" si="1"/>
-        <v>86.04</v>
+      <c r="B16" s="8">
+        <f t="shared" si="1"/>
+        <v>75.239999999999995</v>
       </c>
       <c r="C16" s="6">
         <v>6</v>
@@ -1763,7 +1809,7 @@
       </c>
       <c r="P16" s="7">
         <f t="shared" si="2"/>
-        <v>86.04</v>
+        <v>75.239999999999995</v>
       </c>
       <c r="Q16" s="1" t="s">
         <v>37</v>
@@ -1773,9 +1819,9 @@
       <c r="A17" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="9">
-        <f t="shared" si="1"/>
-        <v>100.38000000000001</v>
+      <c r="B17" s="8">
+        <f t="shared" si="1"/>
+        <v>100.32</v>
       </c>
       <c r="C17" s="6">
         <v>6</v>
@@ -1798,13 +1844,16 @@
       <c r="I17" s="6">
         <v>6</v>
       </c>
+      <c r="J17" s="6">
+        <v>6</v>
+      </c>
       <c r="O17" s="6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P17" s="7">
         <f t="shared" si="2"/>
-        <v>100.38000000000001</v>
+        <v>100.32</v>
       </c>
       <c r="Q17" s="1" t="s">
         <v>36</v>
@@ -1814,9 +1863,9 @@
       <c r="A18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="9">
-        <f t="shared" si="1"/>
-        <v>100.38000000000001</v>
+      <c r="B18" s="8">
+        <f t="shared" si="1"/>
+        <v>100.32</v>
       </c>
       <c r="C18" s="6">
         <v>6</v>
@@ -1839,13 +1888,16 @@
       <c r="I18" s="6">
         <v>6</v>
       </c>
+      <c r="J18" s="6">
+        <v>6</v>
+      </c>
       <c r="O18" s="6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P18" s="7">
         <f t="shared" si="2"/>
-        <v>100.38000000000001</v>
+        <v>100.32</v>
       </c>
       <c r="Q18" s="1" t="s">
         <v>36</v>
@@ -1855,9 +1907,9 @@
       <c r="A19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="9">
-        <f t="shared" si="1"/>
-        <v>100.38000000000001</v>
+      <c r="B19" s="8">
+        <f t="shared" si="1"/>
+        <v>100.32</v>
       </c>
       <c r="C19" s="6">
         <v>6</v>
@@ -1880,13 +1932,16 @@
       <c r="I19" s="6">
         <v>6</v>
       </c>
+      <c r="J19" s="6">
+        <v>6</v>
+      </c>
       <c r="O19" s="6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P19" s="7">
         <f t="shared" si="2"/>
-        <v>100.38000000000001</v>
+        <v>100.32</v>
       </c>
       <c r="Q19" s="1" t="s">
         <v>36</v>
@@ -1896,9 +1951,9 @@
       <c r="A20" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="9">
-        <f t="shared" si="1"/>
-        <v>71.7</v>
+      <c r="B20" s="8">
+        <f t="shared" si="1"/>
+        <v>62.699999999999996</v>
       </c>
       <c r="C20" s="6">
         <v>6</v>
@@ -1927,7 +1982,7 @@
       </c>
       <c r="P20" s="7">
         <f t="shared" si="2"/>
-        <v>71.7</v>
+        <v>62.699999999999996</v>
       </c>
       <c r="Q20" s="1" t="s">
         <v>38</v>
@@ -1937,9 +1992,9 @@
       <c r="A21" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="9">
-        <f t="shared" si="1"/>
-        <v>100.38000000000001</v>
+      <c r="B21" s="8">
+        <f t="shared" si="1"/>
+        <v>102.41</v>
       </c>
       <c r="C21" s="6">
         <v>6</v>
@@ -1962,13 +2017,16 @@
       <c r="I21" s="6">
         <v>6</v>
       </c>
+      <c r="J21" s="6">
+        <v>7</v>
+      </c>
       <c r="O21" s="6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P21" s="7">
         <f t="shared" si="2"/>
-        <v>100.38000000000001</v>
+        <v>102.41</v>
       </c>
       <c r="Q21" s="1" t="s">
         <v>36</v>
@@ -1978,9 +2036,9 @@
       <c r="A22" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="9">
-        <f t="shared" si="1"/>
-        <v>86.04</v>
+      <c r="B22" s="8">
+        <f t="shared" si="1"/>
+        <v>87.78</v>
       </c>
       <c r="C22" s="6">
         <v>6</v>
@@ -2000,13 +2058,19 @@
       <c r="H22" s="6">
         <v>6</v>
       </c>
+      <c r="I22" s="6">
+        <v>0</v>
+      </c>
+      <c r="J22" s="6">
+        <v>6</v>
+      </c>
       <c r="O22" s="6">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="P22" s="7">
         <f t="shared" si="2"/>
-        <v>86.04</v>
+        <v>87.78</v>
       </c>
       <c r="Q22" s="1" t="s">
         <v>36</v>
@@ -2016,9 +2080,9 @@
       <c r="A23" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="9">
-        <f t="shared" si="1"/>
-        <v>86.04</v>
+      <c r="B23" s="8">
+        <f t="shared" si="1"/>
+        <v>87.78</v>
       </c>
       <c r="C23" s="6">
         <v>6</v>
@@ -2041,13 +2105,16 @@
       <c r="I23" s="6">
         <v>6</v>
       </c>
+      <c r="J23" s="6">
+        <v>6</v>
+      </c>
       <c r="O23" s="6">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="P23" s="7">
         <f t="shared" si="2"/>
-        <v>86.04</v>
+        <v>87.78</v>
       </c>
       <c r="Q23" s="1" t="s">
         <v>37</v>
@@ -2057,9 +2124,9 @@
       <c r="A24" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="9">
-        <f t="shared" si="1"/>
-        <v>100.38000000000001</v>
+      <c r="B24" s="8">
+        <f t="shared" si="1"/>
+        <v>100.32</v>
       </c>
       <c r="C24" s="6">
         <v>6</v>
@@ -2082,13 +2149,16 @@
       <c r="I24" s="6">
         <v>6</v>
       </c>
+      <c r="J24" s="6">
+        <v>6</v>
+      </c>
       <c r="O24" s="6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P24" s="7">
         <f t="shared" si="2"/>
-        <v>100.38000000000001</v>
+        <v>100.32</v>
       </c>
       <c r="Q24" s="1" t="s">
         <v>36</v>
@@ -2098,9 +2168,9 @@
       <c r="A25" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="9">
-        <f t="shared" si="1"/>
-        <v>100.38000000000001</v>
+      <c r="B25" s="8">
+        <f t="shared" si="1"/>
+        <v>87.78</v>
       </c>
       <c r="C25" s="6">
         <v>6</v>
@@ -2129,7 +2199,7 @@
       </c>
       <c r="P25" s="7">
         <f t="shared" si="2"/>
-        <v>100.38000000000001</v>
+        <v>87.78</v>
       </c>
       <c r="Q25" s="1" t="s">
         <v>36</v>
@@ -2139,9 +2209,9 @@
       <c r="A26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="9">
-        <f t="shared" si="1"/>
-        <v>100.38000000000001</v>
+      <c r="B26" s="8">
+        <f t="shared" si="1"/>
+        <v>100.32</v>
       </c>
       <c r="C26" s="6">
         <v>6</v>
@@ -2164,13 +2234,16 @@
       <c r="I26" s="6">
         <v>6</v>
       </c>
+      <c r="J26" s="6">
+        <v>6</v>
+      </c>
       <c r="O26" s="6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P26" s="7">
         <f t="shared" si="2"/>
-        <v>100.38000000000001</v>
+        <v>100.32</v>
       </c>
       <c r="Q26" s="1" t="s">
         <v>36</v>
@@ -2180,9 +2253,9 @@
       <c r="A27" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="9">
-        <f t="shared" si="1"/>
-        <v>100.38000000000001</v>
+      <c r="B27" s="8">
+        <f t="shared" si="1"/>
+        <v>87.78</v>
       </c>
       <c r="C27" s="6">
         <v>6</v>
@@ -2211,7 +2284,7 @@
       </c>
       <c r="P27" s="7">
         <f t="shared" si="2"/>
-        <v>100.38000000000001</v>
+        <v>87.78</v>
       </c>
       <c r="Q27" s="1" t="s">
         <v>36</v>
@@ -2221,9 +2294,9 @@
       <c r="A28" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="9">
-        <f t="shared" si="1"/>
-        <v>100.38000000000001</v>
+      <c r="B28" s="8">
+        <f t="shared" si="1"/>
+        <v>100.32</v>
       </c>
       <c r="C28" s="6">
         <v>6</v>
@@ -2246,13 +2319,16 @@
       <c r="I28" s="6">
         <v>6</v>
       </c>
+      <c r="J28" s="6">
+        <v>6</v>
+      </c>
       <c r="O28" s="6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P28" s="7">
         <f t="shared" si="2"/>
-        <v>100.38000000000001</v>
+        <v>100.32</v>
       </c>
       <c r="Q28" s="1" t="s">
         <v>36</v>
@@ -2262,9 +2338,9 @@
       <c r="A29" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="9">
-        <f t="shared" si="1"/>
-        <v>71.7</v>
+      <c r="B29" s="8">
+        <f t="shared" si="1"/>
+        <v>62.699999999999996</v>
       </c>
       <c r="C29" s="6">
         <v>0</v>
@@ -2284,13 +2360,16 @@
       <c r="H29" s="6">
         <v>6</v>
       </c>
+      <c r="I29" s="6">
+        <v>0</v>
+      </c>
       <c r="O29" s="6">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="P29" s="7">
         <f t="shared" si="2"/>
-        <v>71.7</v>
+        <v>62.699999999999996</v>
       </c>
       <c r="Q29" s="1" t="s">
         <v>37</v>
@@ -2300,9 +2379,9 @@
       <c r="A30" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="9">
-        <f t="shared" si="1"/>
-        <v>100.38000000000001</v>
+      <c r="B30" s="8">
+        <f t="shared" si="1"/>
+        <v>100.32</v>
       </c>
       <c r="C30" s="6">
         <v>6</v>
@@ -2325,13 +2404,16 @@
       <c r="I30" s="6">
         <v>6</v>
       </c>
+      <c r="J30" s="6">
+        <v>6</v>
+      </c>
       <c r="O30" s="6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="P30" s="7">
         <f t="shared" si="2"/>
-        <v>100.38000000000001</v>
+        <v>100.32</v>
       </c>
       <c r="Q30" s="1" t="s">
         <v>36</v>
@@ -2341,9 +2423,9 @@
       <c r="A31" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="9">
-        <f t="shared" si="1"/>
-        <v>100.38000000000001</v>
+      <c r="B31" s="8">
+        <f t="shared" si="1"/>
+        <v>102.41</v>
       </c>
       <c r="C31" s="6">
         <v>6</v>
@@ -2366,13 +2448,16 @@
       <c r="I31" s="6">
         <v>6</v>
       </c>
+      <c r="J31" s="6">
+        <v>7</v>
+      </c>
       <c r="O31" s="6">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="P31" s="7">
         <f t="shared" si="2"/>
-        <v>100.38000000000001</v>
+        <v>102.41</v>
       </c>
       <c r="Q31" s="1" t="s">
         <v>36</v>
